--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
@@ -8,20 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49DCEF93-3A42-4003-8B0D-E44EECAA5117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C2E571-8603-4132-B526-569AED43B12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification" sheetId="1" r:id="rId1"/>
     <sheet name="TAN" sheetId="2" r:id="rId2"/>
     <sheet name="DM" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -30,6 +41,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={C0AD1AD3-AB14-4363-AEE7-2707F52F4B90}</author>
+    <author>tc={4819A022-46B5-40C6-A929-5AE7C3ABFFC2}</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{C0AD1AD3-AB14-4363-AEE7-2707F52F4B90}">
@@ -38,7 +50,7 @@
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     General observations:
-- all samples slowly increased pH while exposed
+- all samples slowly increased pH while exposed to air
 - No foaming observed
 - AA had considerable buffer capacity around pH of 6.5
 Method:
@@ -47,12 +59,50 @@
 - added 100 μL in 1 min intervals to allow solution to restabilize </t>
       </text>
     </comment>
+    <comment ref="E1" authorId="1" shapeId="0" xr:uid="{4819A022-46B5-40C6-A929-5AE7C3ABFFC2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Other meassurements were done the day before the exp
+Actual meausrement time was 10:17</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={A485F1A9-0466-436B-B751-AA6178C6D399}</author>
+    <author>tc={13C12FA9-EEBF-47E4-BBD0-D59E8ABE06C6}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{A485F1A9-0466-436B-B751-AA6178C6D399}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    AA = Acetic acid
+H = H2SO4
+U = Untreated</t>
+      </text>
+    </comment>
+    <comment ref="B11" authorId="1" shapeId="0" xr:uid="{13C12FA9-EEBF-47E4-BBD0-D59E8ABE06C6}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Same amount of water added - i.e. not the same dilution factor as the other samples</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>ID</t>
   </si>
@@ -79,14 +129,66 @@
   </si>
   <si>
     <t>V(acid) [mL]</t>
+  </si>
+  <si>
+    <t>pH(at aplication)</t>
+  </si>
+  <si>
+    <t>m(sample) [g]</t>
+  </si>
+  <si>
+    <t>AA1</t>
+  </si>
+  <si>
+    <t>AA2</t>
+  </si>
+  <si>
+    <t>AA3</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>STD1</t>
+  </si>
+  <si>
+    <t>STD2</t>
+  </si>
+  <si>
+    <t>m expected [g]</t>
+  </si>
+  <si>
+    <t>Dilution factor [-]</t>
+  </si>
+  <si>
+    <t>c NH4-N (diluted) [mg/L]</t>
+  </si>
+  <si>
+    <t>NH4-N (sample) [g/L]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -131,10 +233,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,7 +527,7 @@
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="A1" dT="2026-02-18T14:34:07.79" personId="{298C596E-E9DF-4FAE-B6FA-67EB1BFD5A54}" id="{C0AD1AD3-AB14-4363-AEE7-2707F52F4B90}">
     <text xml:space="preserve">General observations:
-- all samples slowly increased pH while exposed
+- all samples slowly increased pH while exposed to air
 - No foaming observed
 - AA had considerable buffer capacity around pH of 6.5
 Method:
@@ -431,6 +535,23 @@
 - AA, added amount to math pH-level of H2O4
 - added 100 μL in 1 min intervals to allow solution to restabilize </text>
   </threadedComment>
+  <threadedComment ref="E1" dT="2026-02-22T14:08:42.71" personId="{298C596E-E9DF-4FAE-B6FA-67EB1BFD5A54}" id="{4819A022-46B5-40C6-A929-5AE7C3ABFFC2}">
+    <text>Other meassurements were done the day before the exp
+Actual meausrement time was 10:17</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-22T14:16:25.16" personId="{298C596E-E9DF-4FAE-B6FA-67EB1BFD5A54}" id="{A485F1A9-0466-436B-B751-AA6178C6D399}">
+    <text>AA = Acetic acid
+H = H2SO4
+U = Untreated</text>
+  </threadedComment>
+  <threadedComment ref="B11" dT="2026-02-22T14:19:08.25" personId="{298C596E-E9DF-4FAE-B6FA-67EB1BFD5A54}" id="{13C12FA9-EEBF-47E4-BBD0-D59E8ABE06C6}">
+    <text>Same amount of water added - i.e. not the same dilution factor as the other samples</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -439,9 +560,10 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -451,11 +573,14 @@
       <c r="B1" t="s">
         <v>4</v>
       </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
       <c r="D1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F1" t="s">
         <v>8</v>
@@ -468,11 +593,14 @@
       <c r="B2">
         <v>500.03800000000001</v>
       </c>
+      <c r="C2">
+        <v>7.02</v>
+      </c>
       <c r="D2">
-        <v>7.02</v>
+        <v>6.02</v>
       </c>
       <c r="E2">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="F2" s="2">
         <v>0.79</v>
@@ -485,11 +613,14 @@
       <c r="B3">
         <v>500.048</v>
       </c>
+      <c r="C3">
+        <v>7.01</v>
+      </c>
       <c r="D3">
-        <v>7.01</v>
+        <v>6.01</v>
       </c>
       <c r="E3">
-        <v>6.01</v>
+        <v>6.12</v>
       </c>
       <c r="F3" s="2">
         <v>1.75</v>
@@ -502,11 +633,14 @@
       <c r="B4">
         <v>500.02</v>
       </c>
-      <c r="D4">
+      <c r="C4">
         <v>6.97</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D4" t="s">
         <v>7</v>
+      </c>
+      <c r="E4">
+        <v>7.03</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -519,11 +653,251 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CE6BAF-82F2-4D49-ABBC-1E07DACE7AB7}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CE6BAF-82F2-4D49-ABBC-1E07DACE7AB7}">
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1.052</v>
+      </c>
+      <c r="C2">
+        <v>72</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>50</v>
+      </c>
+      <c r="F2" s="4">
+        <f>((C2*D2*E2)/B2)/1000</f>
+        <v>3.422053231939163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>1.0044999999999999</v>
+      </c>
+      <c r="C3">
+        <v>72</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>50</v>
+      </c>
+      <c r="F3" s="4">
+        <f t="shared" ref="F3:F10" si="0">((C3*D3*E3)/B3)/1000</f>
+        <v>3.5838725734196117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>1.0115000000000001</v>
+      </c>
+      <c r="C4">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>3.1636183885318832</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>1.0355000000000001</v>
+      </c>
+      <c r="C5">
+        <v>71</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5" s="4">
+        <f t="shared" si="0"/>
+        <v>3.428295509415741</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>1.0290999999999999</v>
+      </c>
+      <c r="C6">
+        <v>72</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>50</v>
+      </c>
+      <c r="F6" s="4">
+        <f t="shared" si="0"/>
+        <v>3.498202312700418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>1.0528999999999999</v>
+      </c>
+      <c r="C7">
+        <v>69</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4">
+        <f t="shared" si="0"/>
+        <v>3.2766644505651059</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>1.0108999999999999</v>
+      </c>
+      <c r="C8">
+        <v>71</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8" s="4">
+        <f t="shared" si="0"/>
+        <v>3.5117222277178755</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>1.0511999999999999</v>
+      </c>
+      <c r="C9">
+        <v>75</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+      <c r="F9" s="4">
+        <f t="shared" si="0"/>
+        <v>3.5673515981735164</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>1.0076000000000001</v>
+      </c>
+      <c r="C10">
+        <v>66</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>50</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" si="0"/>
+        <v>3.2751091703056767</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>0.50839999999999996</v>
+      </c>
+      <c r="C11">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>0.50829999999999997</v>
+      </c>
+      <c r="C12">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4C2E571-8603-4132-B526-569AED43B12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B187498-50D2-4183-8221-853E364BE522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification" sheetId="1" r:id="rId1"/>
@@ -101,8 +101,27 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={2CC04251-676B-4A70-98C9-6C16A86A16B9}</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{2CC04251-676B-4A70-98C9-6C16A86A16B9}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    %DM during field exp were also around 6-7 % 
+I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>ID</t>
   </si>
@@ -180,15 +199,49 @@
   </si>
   <si>
     <t>NH4-N (sample) [g/L]</t>
+  </si>
+  <si>
+    <t>m(alue) [g]</t>
+  </si>
+  <si>
+    <t>u1</t>
+  </si>
+  <si>
+    <t>u2</t>
+  </si>
+  <si>
+    <t>u3</t>
+  </si>
+  <si>
+    <t>m(wet + alue) [g]</t>
+  </si>
+  <si>
+    <t>m(wet)</t>
+  </si>
+  <si>
+    <t>m(dry + alue) [g]</t>
+  </si>
+  <si>
+    <t>m(dry)</t>
+  </si>
+  <si>
+    <t>%DM</t>
+  </si>
+  <si>
+    <t>%DM std-dev</t>
+  </si>
+  <si>
+    <t>%DM avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -210,7 +263,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -233,12 +286,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,6 +609,15 @@
 </ThreadedComments>
 </file>
 
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="H1" dT="2026-02-25T10:01:20.20" personId="{298C596E-E9DF-4FAE-B6FA-67EB1BFD5A54}" id="{2CC04251-676B-4A70-98C9-6C16A86A16B9}">
+    <text>%DM during field exp were also around 6-7 % 
+I am yet again surprised the variance in the acidified samples are smaller, however in this case it might be better explaned by the lower mass of these samples</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
@@ -902,10 +965,305 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C33D55-02E8-4C35-A092-3068BFF0F42C}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84C33D55-02E8-4C35-A092-3068BFF0F42C}">
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
+        <v>4.2729999999999997</v>
+      </c>
+      <c r="C2">
+        <v>29.349</v>
+      </c>
+      <c r="D2">
+        <f>C2-B2</f>
+        <v>25.076000000000001</v>
+      </c>
+      <c r="E2">
+        <v>5.3280000000000003</v>
+      </c>
+      <c r="F2">
+        <f>E2-B2</f>
+        <v>1.0550000000000006</v>
+      </c>
+      <c r="G2" s="2">
+        <f>(F2/D2)*100</f>
+        <v>4.2072100813526898</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
+        <v>4.266</v>
+      </c>
+      <c r="C3">
+        <v>31.917000000000002</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D10" si="0">C3-B3</f>
+        <v>27.651000000000003</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5.85</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F10" si="1">E3-B3</f>
+        <v>1.5839999999999996</v>
+      </c>
+      <c r="G3" s="2">
+        <f t="shared" ref="G3:G10" si="2">(F3/D3)*100</f>
+        <v>5.7285450797439488</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>4.2619999999999996</v>
+      </c>
+      <c r="C4" s="2">
+        <v>23.88</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>19.617999999999999</v>
+      </c>
+      <c r="E4">
+        <v>5.5839999999999996</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>1.3220000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <f t="shared" si="2"/>
+        <v>6.7387093485574479</v>
+      </c>
+      <c r="H4" s="5">
+        <f>AVERAGE(G2:G4)</f>
+        <v>5.5581548365513624</v>
+      </c>
+      <c r="I4" s="2">
+        <f>_xlfn.STDEV.P(G2:G4)</f>
+        <v>1.0404796205583828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>4.2690000000000001</v>
+      </c>
+      <c r="C5">
+        <v>49.179000000000002</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>44.910000000000004</v>
+      </c>
+      <c r="E5">
+        <v>6.6079999999999997</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>2.3389999999999995</v>
+      </c>
+      <c r="G5" s="2">
+        <f t="shared" si="2"/>
+        <v>5.2081941661099966</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>4.2610000000000001</v>
+      </c>
+      <c r="C6">
+        <v>67.694000000000003</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>63.433</v>
+      </c>
+      <c r="E6" s="2">
+        <v>7.74</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>3.4790000000000001</v>
+      </c>
+      <c r="G6" s="2">
+        <f t="shared" si="2"/>
+        <v>5.4845269812242838</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>4.2649999999999997</v>
+      </c>
+      <c r="C7">
+        <v>53.735999999999997</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>49.470999999999997</v>
+      </c>
+      <c r="E7">
+        <v>6.798</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>2.5330000000000004</v>
+      </c>
+      <c r="G7" s="2">
+        <f t="shared" si="2"/>
+        <v>5.1201714135554175</v>
+      </c>
+      <c r="H7" s="5">
+        <f>AVERAGE(G5:G7)</f>
+        <v>5.2709641869632327</v>
+      </c>
+      <c r="I7" s="2">
+        <f>_xlfn.STDEV.P(G5:G7)</f>
+        <v>0.15522843717408272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="C8">
+        <v>44.493000000000002</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>40.222999999999999</v>
+      </c>
+      <c r="E8">
+        <v>6.375</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>2.1050000000000004</v>
+      </c>
+      <c r="G8" s="2">
+        <f t="shared" si="2"/>
+        <v>5.2333242174875085</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9">
+        <v>4.2709999999999999</v>
+      </c>
+      <c r="C9">
+        <v>70.081000000000003</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>65.81</v>
+      </c>
+      <c r="E9">
+        <v>7.782</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>3.5110000000000001</v>
+      </c>
+      <c r="G9" s="2">
+        <f t="shared" si="2"/>
+        <v>5.3350554626956388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10">
+        <v>4.28</v>
+      </c>
+      <c r="C10">
+        <v>49.945</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>45.664999999999999</v>
+      </c>
+      <c r="E10">
+        <v>7.3010000000000002</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="G10" s="2">
+        <f t="shared" si="2"/>
+        <v>6.6155699113106312</v>
+      </c>
+      <c r="H10" s="5">
+        <f>AVERAGE(G8:G10)</f>
+        <v>5.7279831971645931</v>
+      </c>
+      <c r="I10" s="2">
+        <f>_xlfn.STDEV.P(G8:G10)</f>
+        <v>0.62899122564591436</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B187498-50D2-4183-8221-853E364BE522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4402BB1F-84E8-4B86-A4E5-70EBE1037BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification" sheetId="1" r:id="rId1"/>
@@ -241,9 +241,9 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,12 +258,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -292,7 +286,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -785,7 +779,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" ref="F3:F10" si="0">((C3*D3*E3)/B3)/1000</f>
+        <f t="shared" ref="F3:F12" si="0">((C3*D3*E3)/B3)/1000</f>
         <v>3.5838725734196117</v>
       </c>
     </row>
@@ -946,6 +940,16 @@
       <c r="C11">
         <v>35</v>
       </c>
+      <c r="D11" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E11">
+        <v>99</v>
+      </c>
+      <c r="F11" s="4">
+        <f t="shared" si="0"/>
+        <v>3.4077498033044851</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -956,6 +960,16 @@
       </c>
       <c r="C12">
         <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E12">
+        <v>99</v>
+      </c>
+      <c r="F12" s="4">
+        <f t="shared" si="0"/>
+        <v>3.7005705292150304</v>
       </c>
     </row>
   </sheetData>
@@ -971,7 +985,7 @@
   <cols>
     <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
+++ b/Lab-trails/2026-02-19-pig-slurry/2026-02-19-pig-slurry.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikae\Desktop\Github - speciale\Larsen-2025-Masterthesis-DFCs\Lab-trails\2026-02-19-pig-slurry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4402BB1F-84E8-4B86-A4E5-70EBE1037BAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E7F56BA-B150-4A85-9E6C-7A20ECF032CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acidification" sheetId="1" r:id="rId1"/>
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -232,6 +232,41 @@
   </si>
   <si>
     <t>%DM avg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N (sample) [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Mean </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">NH4-N (sample) [g/L] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>stdev</t>
+    </r>
+  </si>
+  <si>
+    <t>NAN</t>
   </si>
 </sst>
 </file>
@@ -711,7 +746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CE6BAF-82F2-4D49-ABBC-1E07DACE7AB7}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.109375" bestFit="1" customWidth="1"/>
@@ -719,9 +754,11 @@
     <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -740,8 +777,14 @@
       <c r="F1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -762,7 +805,7 @@
         <v>3.422053231939163</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -783,7 +826,7 @@
         <v>3.5838725734196117</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -803,8 +846,16 @@
         <f t="shared" si="0"/>
         <v>3.1636183885318832</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="4">
+        <f>AVERAGE(F2:F4)</f>
+        <v>3.3898480646302196</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.STDEV.P(F2:F4)</f>
+        <v>0.17307276808702957</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -825,7 +876,7 @@
         <v>3.428295509415741</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -846,7 +897,7 @@
         <v>3.498202312700418</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -866,8 +917,16 @@
         <f t="shared" si="0"/>
         <v>3.2766644505651059</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G7" s="4">
+        <f>AVERAGE(F5:F7)</f>
+        <v>3.401054090893755</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.STDEV.P(F5:F7)</f>
+        <v>9.2470994559334274E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -888,7 +947,7 @@
         <v>3.5117222277178755</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -909,7 +968,7 @@
         <v>3.5673515981735164</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -929,8 +988,16 @@
         <f t="shared" si="0"/>
         <v>3.2751091703056767</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G10" s="4">
+        <f>AVERAGE(F8:F10)</f>
+        <v>3.4513943320656892</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.STDEV.P(F8:F10)</f>
+        <v>0.12670438142092311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -951,7 +1018,7 @@
         <v>3.4077498033044851</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -968,8 +1035,15 @@
         <v>99</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" si="0"/>
+        <f>((C12*D12*E12)/B12)/1000</f>
         <v>3.7005705292150304</v>
+      </c>
+      <c r="G12" s="4">
+        <f>AVERAGE(F11:F12)</f>
+        <v>3.5541601662597575</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
